--- a/MATH/M12/bus123-math-m12-l01-starter.xlsx
+++ b/MATH/M12/bus123-math-m12-l01-starter.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A7C9A3-025D-994C-B94D-BD5DE4EF6134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="29720" windowHeight="19940" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -748,52 +748,16 @@
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -809,61 +773,97 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1128,6 +1128,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C1635B81-F21B-7E49-97B5-4B3396293704}">
+  <we:reference id="wa200010215" version="2.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010215" version="2.0.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -1143,110 +1163,110 @@
   <sheetData>
     <row r="1" spans="2:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="35"/>
     </row>
     <row r="3" spans="2:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="2:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="36"/>
     </row>
     <row r="5" spans="2:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="32"/>
     </row>
     <row r="7" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="11"/>
+      <c r="C12" s="32"/>
     </row>
     <row r="13" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1277,526 +1297,526 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="3" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="8">
         <v>12</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="8">
         <v>15</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="8">
         <v>18</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="8">
         <v>11</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="8">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
     </row>
     <row r="9" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
     </row>
     <row r="10" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
     <row r="11" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="23" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="16" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
     </row>
     <row r="18" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
     </row>
     <row r="19" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
     </row>
     <row r="21" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
     </row>
     <row r="23" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
     </row>
     <row r="24" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="8">
         <v>4</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
     </row>
     <row r="25" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="8">
         <v>6</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="8">
         <v>8</v>
       </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
     </row>
     <row r="27" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="8">
         <v>10</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
     </row>
     <row r="28" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="8">
         <v>12</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
     </row>
     <row r="29" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
     </row>
     <row r="30" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="14"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="3"/>
     </row>
     <row r="31" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
     </row>
     <row r="32" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
     <row r="33" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="23" t="s">
+      <c r="C33" s="2"/>
+      <c r="D33" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
     </row>
     <row r="34" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="23" t="s">
+      <c r="C34" s="2"/>
+      <c r="D34" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
     </row>
     <row r="36" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="37" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
     </row>
     <row r="38" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="8">
         <v>12</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="8">
         <v>8.4</v>
       </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="8">
         <v>15</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="8">
         <v>7.9</v>
       </c>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="8">
         <v>10</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="8">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="8">
         <v>22</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="8">
         <v>6.5</v>
       </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="8">
         <v>30</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="8">
         <v>5.2</v>
       </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="8">
         <v>8</v>
       </c>
-      <c r="D44" s="20">
+      <c r="D44" s="8">
         <v>9.1</v>
       </c>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="20">
+      <c r="C45" s="8">
         <v>18</v>
       </c>
-      <c r="D45" s="20">
+      <c r="D45" s="8">
         <v>7.1</v>
       </c>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
     </row>
     <row r="47" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="18" t="s">
+      <c r="B52" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1828,232 +1848,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="3" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="8">
         <v>148000</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="8">
         <v>152000</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="8">
         <v>161000</v>
       </c>
-      <c r="F5" s="22"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="8">
         <v>82000</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="8">
         <v>79000</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="8">
         <v>85000</v>
       </c>
-      <c r="F6" s="22"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="8">
         <v>95000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="8">
         <v>99000</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="8">
         <v>102000</v>
       </c>
-      <c r="F7" s="22"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="8">
         <v>28000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="8">
         <v>31000</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="8">
         <v>27000</v>
       </c>
-      <c r="F8" s="22"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="2:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="2:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
     </row>
     <row r="13" spans="2:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
     </row>
     <row r="17" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
     </row>
     <row r="19" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
     </row>
     <row r="20" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
     </row>
     <row r="21" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C21:D21"/>
@@ -2064,11 +2089,6 @@
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2091,240 +2111,240 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" spans="2:5" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="7" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="15" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="15" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="15" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="15" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="15" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
     </row>
     <row r="14" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="19" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="19" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="19" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
     </row>
     <row r="19" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="23" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
     </row>
     <row r="22" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="27" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="7">
